--- a/ipo_data.xlsx
+++ b/ipo_data.xlsx
@@ -413,76 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>open_date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>close_date</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Innovision IPO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>12 Mar 2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>₹521-548</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Rajputana Stainless IPO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>09 Mar 2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>11 Mar 2026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>₹116-122</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ipo_data.xlsx
+++ b/ipo_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/ipo_data.xlsx
+++ b/ipo_data.xlsx
@@ -413,9 +413,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>open_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>close_date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GSP Crop Science Limited</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>